--- a/StructureDefinition-discharge-medication-request-profile.xlsx
+++ b/StructureDefinition-discharge-medication-request-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T10:04:33+00:00</t>
+    <t>2026-02-09T10:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-discharge-medication-request-profile.xlsx
+++ b/StructureDefinition-discharge-medication-request-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2421" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2421" uniqueCount="487">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T10:35:12+00:00</t>
+    <t>2026-10-27T13:25:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1302,6 +1302,10 @@
   </si>
   <si>
     <t>The amount or quantity to provide as part of the first dispense.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>Supply.quantity[moodCode=RQO]</t>
@@ -7603,7 +7607,7 @@
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>404</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -7615,7 +7619,7 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -7623,10 +7627,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7649,13 +7653,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7706,7 +7710,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7730,7 +7734,7 @@
         <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -7738,10 +7742,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7764,13 +7768,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7821,7 +7825,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7845,7 +7849,7 @@
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -7853,10 +7857,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7882,16 +7886,16 @@
         <v>361</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7940,7 +7944,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7958,13 +7962,13 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -7972,10 +7976,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7998,16 +8002,16 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8057,7 +8061,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8075,24 +8079,24 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8118,10 +8122,10 @@
         <v>401</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8172,7 +8176,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8184,30 +8188,30 @@
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>404</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8230,16 +8234,16 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8289,7 +8293,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8307,13 +8311,13 @@
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8321,10 +8325,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8347,13 +8351,13 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8404,7 +8408,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8428,7 +8432,7 @@
         <v>320</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8436,10 +8440,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8465,10 +8469,10 @@
         <v>348</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8519,7 +8523,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8543,7 +8547,7 @@
         <v>20</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -8551,10 +8555,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8580,10 +8584,10 @@
         <v>189</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8614,7 +8618,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8632,7 +8636,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8656,7 +8660,7 @@
         <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -8664,10 +8668,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8693,10 +8697,10 @@
         <v>372</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8747,7 +8751,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8765,13 +8769,13 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -8779,10 +8783,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8894,10 +8898,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9011,10 +9015,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9130,10 +9134,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9156,16 +9160,16 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9191,13 +9195,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -9215,7 +9219,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>90</v>
@@ -9233,24 +9237,24 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9276,10 +9280,10 @@
         <v>189</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9309,10 +9313,10 @@
         <v>193</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9330,7 +9334,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9354,18 +9358,18 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9388,16 +9392,16 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9447,7 +9451,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9462,7 +9466,7 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>20</v>
@@ -9471,7 +9475,7 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>

--- a/StructureDefinition-discharge-medication-request-profile.xlsx
+++ b/StructureDefinition-discharge-medication-request-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:25:43+00:00</t>
+    <t>2026-10-27T13:28:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
